--- a/data/trans_orig/IP38E_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP38E_2023-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31048</t>
+          <t>30835</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37431</t>
+          <t>37365</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38548</t>
+          <t>38684</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43476</t>
+          <t>43486</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72351</t>
+          <t>72304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79948</t>
+          <t>80171</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3681</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49749</t>
+          <t>49555</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58108</t>
+          <t>57826</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58576</t>
+          <t>58564</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69968</t>
+          <t>70221</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>112623</t>
+          <t>111723</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126228</t>
+          <t>125738</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10541</t>
+          <t>10735</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15983</t>
+          <t>15995</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>23126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27274</t>
+          <t>29258</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42418</t>
+          <t>42686</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47621</t>
+          <t>47374</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54113</t>
+          <t>53977</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77839</t>
+          <t>79674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95384</t>
+          <t>94928</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21025</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26087</t>
+          <t>24252</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35272</t>
+          <t>35247</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43698</t>
+          <t>43832</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48289</t>
+          <t>48143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58759</t>
+          <t>58481</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87420</t>
+          <t>86409</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101129</t>
+          <t>100593</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,56%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12457</t>
+          <t>12482</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15059</t>
+          <t>15205</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>10484</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23657</t>
+          <t>24668</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>157227</t>
+          <t>157476</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>176039</t>
+          <t>176004</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>202410</t>
+          <t>202587</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>220819</t>
+          <t>220907</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>368685</t>
+          <t>368776</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>394305</t>
+          <t>392975</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19480</t>
+          <t>19515</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38043</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>17056</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35553</t>
+          <t>35376</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39177</t>
+          <t>40507</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64797</t>
+          <t>64706</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP38E_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP38E_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38680</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35993</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>40131</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>94,83%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>88,24%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>34870</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>30835</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37365</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>88,95%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>78,66%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>41964</t>
+          <t>36251</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38684</t>
+          <t>31698</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43486</t>
+          <t>38883</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>76834</t>
+          <t>74931</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72304</t>
+          <t>69787</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80171</t>
+          <t>78109</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4795</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11,76%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4330</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1835</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8365</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>11,05%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>21,34%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>9241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6797</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11325</t>
+          <t>11941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>40788</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>40788</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>40788</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>39200</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>39200</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>39200</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44429</t>
+          <t>40939</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44429</t>
+          <t>40939</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44429</t>
+          <t>40939</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>83629</t>
+          <t>81728</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83629</t>
+          <t>81728</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>83629</t>
+          <t>81728</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>60354</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>53865</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>64572</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>87,56%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>78,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>93,68%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>54978</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>49555</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>57826</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>91,19%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>82,19%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>95,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65590</t>
+          <t>53117</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58564</t>
+          <t>48066</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70221</t>
+          <t>56175</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>120568</t>
+          <t>113472</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111723</t>
+          <t>105659</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125738</t>
+          <t>119101</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8575</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4357</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15064</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>12,44%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6,32%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>21,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5312</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2464</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10735</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>17,81%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15995</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>14281</t>
+          <t>14116</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23126</t>
+          <t>21929</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>68929</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>68929</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>68929</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>60290</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>60290</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>60290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>74559</t>
+          <t>58658</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>74559</t>
+          <t>58658</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>74559</t>
+          <t>58658</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>134849</t>
+          <t>127588</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>134849</t>
+          <t>127588</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>134849</t>
+          <t>127588</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>46689</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>42118</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>48685</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>93,17%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>84,04%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>97,15%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>37723</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>29258</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>42686</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>78,1%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>60,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>88,38%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>51861</t>
+          <t>35657</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47374</t>
+          <t>30931</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53977</t>
+          <t>39469</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>89584</t>
+          <t>82345</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79674</t>
+          <t>75282</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94928</t>
+          <t>86640</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3425</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1429</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7996</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>15,96%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>10576</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5613</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19041</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>21,9%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>11,62%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3766</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>12902</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>11601</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24252</t>
+          <t>18664</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>50114</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>50114</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>50114</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>48299</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>48299</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>48299</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55627</t>
+          <t>43833</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55627</t>
+          <t>43833</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55627</t>
+          <t>43833</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>103926</t>
+          <t>93946</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103926</t>
+          <t>93946</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>103926</t>
+          <t>93946</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>51963</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>45408</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>56585</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>85,25%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>74,49%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>92,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>40675</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>35247</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>43832</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>85,22%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>73,85%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>91,83%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>54220</t>
+          <t>41973</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48143</t>
+          <t>36666</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58481</t>
+          <t>45494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>94895</t>
+          <t>93936</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86409</t>
+          <t>86435</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100593</t>
+          <t>100434</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>8992</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12482</t>
+          <t>15547</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>7138</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15205</t>
+          <t>12445</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>16182</t>
+          <t>16130</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10484</t>
+          <t>9632</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24668</t>
+          <t>23631</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>60955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>60955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>60955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>47729</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>47729</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>47729</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>63348</t>
+          <t>49111</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63348</t>
+          <t>49111</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>63348</t>
+          <t>49111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>111077</t>
+          <t>110066</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>111077</t>
+          <t>110066</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>111077</t>
+          <t>110066</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>197686</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>187060</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>203898</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>89,54%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>84,72%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>92,35%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>168247</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>157476</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>176004</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>86,05%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>80,54%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>90,02%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>213635</t>
+          <t>166998</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>202587</t>
+          <t>157881</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>220907</t>
+          <t>174815</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>381882</t>
+          <t>364684</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>368776</t>
+          <t>352379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>392975</t>
+          <t>376801</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23100</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16888</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33726</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10,46%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>15,28%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>27272</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>19515</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>38043</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>13,95%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>19,46%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24328</t>
+          <t>25544</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17056</t>
+          <t>17727</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35376</t>
+          <t>34661</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>51600</t>
+          <t>48644</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40507</t>
+          <t>36527</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64706</t>
+          <t>60949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>220786</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>220786</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>220786</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>195519</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>195519</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>195519</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>237963</t>
+          <t>192542</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>237963</t>
+          <t>192542</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>237963</t>
+          <t>192542</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>433482</t>
+          <t>413328</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>433482</t>
+          <t>413328</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>433482</t>
+          <t>413328</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
